--- a/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
+++ b/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0000000881</t>
+          <t>000000088</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2236468458</t>
+          <t>1236468458</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>000000369</t>
+          <t>0000003694</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>2238289820</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0000005634</t>
+          <t>000000563</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2240427951</t>
+          <t>1240427951</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>000000844</t>
+          <t>0000008447</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1242170137</t>
+          <t>2242170137</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0000011745</t>
+          <t>000001174</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2244387450</t>
+          <t>1244387450</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>000001320</t>
+          <t>0000013200</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1246129634</t>
+          <t>2246129634</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>0000016498</t>
+          <t>000001649</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2248346956</t>
+          <t>1248346956</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>000001795</t>
+          <t>0000017953</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>1250089131</t>
+          <t>2250089131</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">

--- a/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
+++ b/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -172,12 +172,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -234,12 +234,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -249,7 +249,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2017-07-03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -296,12 +296,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -358,12 +358,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -420,12 +420,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>krajoaw instytucja pieniądza elektronicznego</t>
+          <t>krajowa instytucja pieniądza elektronicznego</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>katywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Worcław</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>000000088</t>
+          <t>0000000881</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mała instytucja pieniądza elektronicznego</t>
+          <t/>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2018-10-08</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Astra Finance SA</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-12-03</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1247339575</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1247577145</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2019-12-10</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
+          <t>2018-09-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2238289820</t>
+          <t>1248210665</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2018-10-02</t>
+          <t>2018-02-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1248685807</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Quantum eSrvices sp. z o. o.</t>
+          <t>Zielnoy Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>atkywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>000000563</t>
+          <t>0000005634</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2017-07-03</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4078,12 +4078,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4388,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Legionowo</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Marki</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Otwock</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Radom</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Płock</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -4760,12 +4760,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Zakopane</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Mordarka</t>
         </is>
       </c>
     </row>
@@ -4946,17 +4946,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2019-02-07</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Zielonki</t>
         </is>
       </c>
     </row>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Podłęże</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Tarnów</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>20180425</t>
+          <t/>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t/>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Zgierz</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11-10-2020</t>
+          <t>10-11-2020</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -5442,12 +5442,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Karpacz</t>
         </is>
       </c>
     </row>
@@ -5566,17 +5566,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Lubin</t>
         </is>
       </c>
     </row>
@@ -5628,12 +5628,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Wałbrzych</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o. o.</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2017-12-08</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Helios Markets SP Z O O</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Kalisz</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2242170137</t>
+          <t>1242170137</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Ostrów Wielkopolski</t>
         </is>
       </c>
     </row>
@@ -5938,12 +5938,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nova Data Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1252328545</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Polaris Capital SA</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2018-11-04</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Sopot</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Quantum Services S. A.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Chwaszczyno</t>
         </is>
       </c>
     </row>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2018-02-03</t>
+          <t>2018-03-02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -6248,12 +6248,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Gliwice</t>
         </is>
       </c>
     </row>
@@ -6372,12 +6372,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o. o.</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Helios Markets Sp. z o.o.</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Pruszków</t>
+          <t>Częstochowa</t>
         </is>
       </c>
     </row>
@@ -6496,17 +6496,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2019-11-06</t>
+          <t>2019-06-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Piaseczno</t>
+          <t>Bielsko-Biała</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Wieliczka</t>
+          <t>Niechobrz</t>
         </is>
       </c>
     </row>
@@ -6620,12 +6620,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Oświęcim</t>
+          <t>Przemyśl</t>
         </is>
       </c>
     </row>
@@ -6682,12 +6682,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2017-06-10</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Krosno</t>
+          <t>Sanok</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>wydawca pieniądza elektroniczengo</t>
+          <t>wdyawca pieniądza elektronicznego</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Quantum Services SA</t>
+          <t>Niebieski Canyon SA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>akty</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Mielec</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -6806,17 +6806,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Silesia Invest S. A.</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Świdnica</t>
+          <t>Ogrodniczki</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka Akcyjna</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6898,17 +6898,17 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1253437207</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Hajnówka</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6930,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Gniezno</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -6992,12 +6992,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Leszno</t>
+          <t>Mięćmierz</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7054,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7084,17 +7084,17 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1253674775</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Tczew</t>
+          <t>Biała Podlaska</t>
         </is>
       </c>
     </row>
@@ -7116,17 +7116,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>wykreslony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2018-04-05</t>
+          <t>2018-05-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Wejherowo</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Będzin</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -7302,12 +7302,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Inowrocław</t>
+          <t>Mrągowo</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>2022-04-07</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Grudziądz</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Puławy</t>
+          <t>Kluczbork</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>000001174</t>
+          <t>0000011745</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Zamość</t>
+          <t>Gorzów Wielkopolski</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2017-07-03</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Międzyrzecz</t>
         </is>
       </c>
     </row>
@@ -7736,17 +7736,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Suwałki</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7798,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Nysa</t>
+          <t>Busko-Zdrój</t>
         </is>
       </c>
     </row>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-01-08</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Żary</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -7984,12 +7984,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Świebodzin</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8046,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Kołobrzeg</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -8108,12 +8108,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Stargard</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Astra Finance S. A.</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Sandomierz</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Ostrowiec Świętokrzyski</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Biała Podlaska</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8666,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -8728,12 +8728,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -8852,12 +8852,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -8976,12 +8976,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2246129634</t>
+          <t>1246129634</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9068,17 +9068,17 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1256208855</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -9100,12 +9100,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9259,12 +9259,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9321,12 +9321,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -9348,12 +9348,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>30-12-2025</t>
+          <t/>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -9534,12 +9534,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -9596,17 +9596,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -9782,12 +9782,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>wydawca pieniądza elektronicznego</t>
+          <t>wydawca pieniądza elektroniczneog</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Quantum Serviecs Sp. z o.o.</t>
+          <t>Amber Doradztwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>wyrk</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -9906,12 +9906,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9936,17 +9936,17 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1257317517</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -9968,12 +9968,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1257555085</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Pruszków</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Piaseczno</t>
         </is>
       </c>
     </row>
@@ -10216,17 +10216,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Wieliczka</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10308,17 +10308,17 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>2257792655</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Oświęcim</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10340,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Krosno</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Mielec</t>
         </is>
       </c>
     </row>
@@ -10464,12 +10464,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Świdnica</t>
         </is>
       </c>
     </row>
@@ -10526,12 +10526,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Pruszków</t>
+          <t>Kłodzko</t>
         </is>
       </c>
     </row>
@@ -10588,12 +10588,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Piaseczno</t>
+          <t>Gniezno</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Astra Finance spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>000001649</t>
+          <t>0000016498</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Wieliczka</t>
+          <t>Leszno</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10712,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Oświęcim</t>
+          <t>Tczew</t>
         </is>
       </c>
     </row>
@@ -10774,12 +10774,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Krosno</t>
+          <t>Wejherowo</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Mielec</t>
+          <t>Cieszyn</t>
         </is>
       </c>
     </row>
@@ -10898,12 +10898,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Świdnica</t>
+          <t>Będzin</t>
         </is>
       </c>
     </row>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Inowrocław</t>
         </is>
       </c>
     </row>
@@ -11022,12 +11022,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Gniezno</t>
+          <t>Grudziądz</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Leszno</t>
+          <t>Ostróda</t>
         </is>
       </c>
     </row>
@@ -11146,17 +11146,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -11181,12 +11181,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Tczew</t>
+          <t>Giżycko</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Wejherowo</t>
+          <t>Puławy</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11270,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Zamość</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11332,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Będzin</t>
+          <t>Augustów</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11394,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2017-07-03</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11429,12 +11429,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Inowrocław</t>
+          <t>Suwałki</t>
         </is>
       </c>
     </row>
@@ -11456,12 +11456,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11518,12 +11518,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11553,12 +11553,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Ostróda</t>
+          <t>Brzeg</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Giżycko</t>
+          <t>Żary</t>
         </is>
       </c>
     </row>
@@ -11642,12 +11642,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2019-02-09</t>
+          <t>2019-09-02</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Puławy</t>
+          <t>Świebodzin</t>
         </is>
       </c>
     </row>
@@ -11704,12 +11704,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Zamość</t>
+          <t>Kołobrzeg</t>
         </is>
       </c>
     </row>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Stargard</t>
         </is>
       </c>
     </row>
@@ -11828,12 +11828,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Suwałki</t>
+          <t>Sandomierz</t>
         </is>
       </c>
     </row>
@@ -11890,12 +11890,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Astra Finance Sp. z o.o.</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Nysa</t>
+          <t>Ostrowiec Świętokrzyski</t>
         </is>
       </c>
     </row>
@@ -11952,12 +11952,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2020-10-11</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>0000018535</t>
+          <t>000001853</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -12014,12 +12014,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Żary</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -12076,12 +12076,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -12106,17 +12106,17 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2250089131</t>
+          <t>1250089131</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Świebodzin</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12138,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -12173,12 +12173,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Kołobrzeg</t>
+          <t>Legionowo</t>
         </is>
       </c>
     </row>
@@ -12200,12 +12200,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12235,12 +12235,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Stargard</t>
+          <t>Marki</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Sandomierz</t>
+          <t>Otwock</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12359,12 +12359,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Ostrowiec Świętokrzyski</t>
+          <t>Radom</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Płock</t>
         </is>
       </c>
     </row>
@@ -12448,12 +12448,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
+++ b/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
@@ -125,12 +125,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2015/17/05</t>
+          <t>2021/10/09</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>07-08-2025</t>
+          <t>11-08-2020</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -192,7 +192,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2022-22-07</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -249,12 +249,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2018-20-04</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20230905</t>
+          <t>20170321</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -316,7 +316,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16/03/2024</t>
+          <t>24/02/2021</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023/05/04</t>
+          <t>2020/07/08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -435,12 +435,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2020/24/10</t>
+          <t>2024/24/06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>01-01-2025</t>
+          <t>26-05-2023</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2026-17-08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16/10/2017</t>
+          <t>10/08/2017</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2023/14/10</t>
+          <t>2022/27/08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13-05-2024</t>
+          <t>17-03-2024</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2023-24-01</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2015-17-05</t>
+          <t>2019-27-03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20230704</t>
+          <t>20180225</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20250217</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>03/07/2017</t>
+          <t>26/04/2022</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2018/10/08</t>
+          <t>2026/10/08</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20211103</t>
+          <t>20251120</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>21/10/2024</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2025/18/10</t>
+          <t>2017/14/12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2023/17/01</t>
+          <t>2026/20/07</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2025-20-09</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27/12/2023</t>
+          <t>23/02/2017</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17/05/2015</t>
+          <t>25/04/2022</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025/09/02</t>
+          <t>2021/26/03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2022/25/08</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-23-05</t>
+          <t>2024-25-04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2018-08-10</t>
+          <t>2021-18-06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20190917</t>
+          <t>20250423</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2021/03/11</t>
+          <t>2026/08/02</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2022-12-03</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>27/09/2020</t>
+          <t>19/06/2018</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>24/06/2025</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>27-10-2024</t>
+          <t>14-12-2017</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2018-09-11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2016-24-06</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>12/09/2019</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/08/2018</t>
+          <t>07/06/2020</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020/01/08</t>
+          <t>2019/09/05</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2019/17/09</t>
+          <t>2026/28/09</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23-12-2022</t>
+          <t>15-04-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20241018</t>
+          <t>20200130</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>02/02/2019</t>
+          <t>12/08/2018</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17/01/2023</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2024-22-12</t>
+          <t>2018-01-03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20200724</t>
+          <t>20171211</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20150517</t>
+          <t>20191002</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>11/01/2018</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2025/25/01</t>
+          <t>2019/22/02</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2017/03/07</t>
+          <t>2025/11/05</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>25-08-2022</t>
+          <t>10-11-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2019-17-09</t>
+          <t>2024-28-11</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2024/09/10</t>
+          <t>2017/13/05</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12-04-2019</t>
+          <t>09-02-2018</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2018-21-11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>17/05/2020</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2015/17/05</t>
+          <t>2018/03/07</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>06-01-2019</t>
+          <t>03-06-2017</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>24-06-2016</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>20250226</t>
+          <t>20240713</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2018-10-08 07:37</t>
+          <t>2025-08-10 07:37</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2024/16/01</t>
+          <t>2020/27/05</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2020/24/10</t>
+          <t>2026/25/08</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>03-11-2021</t>
+          <t>11-10-2025</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2019/23/07</t>
+          <t>2018/22/04</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>08-12-2022</t>
+          <t>05-06-2022</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2021-18-03</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2015-17-05</t>
+          <t>2019-06-11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>20220126</t>
+          <t>20181007</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>11/08/2020</t>
+          <t>16/12/2019</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2024/03/10</t>
+          <t>2024/13/05</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2024-29-05</t>
+          <t>2017-21-06</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2020-24-10</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01/03/2019</t>
+          <t>08/01/2019</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2023/30/06</t>
+          <t>2018/13/01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>08-02-2023</t>
+          <t>31-05-2021</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>17/05/2015</t>
+          <t>25/02/2023</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2016/24/06</t>
+          <t>2018/03/02</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>10-11-2020</t>
+          <t>04-01-2017</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>20200329</t>
+          <t>20190123</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20190917</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>12-01-2023</t>
+          <t>25-02-2018</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2023-17-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025/15/09</t>
+          <t>2023/14/12</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>27-11-2022</t>
+          <t>05-02-2017</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>17-05-2015</t>
+          <t>11-01-2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>20240618</t>
+          <t>20230213</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>22/06/2025</t>
+          <t>04/01/2018</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>19-12-2024</t>
+          <t>24-10-2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>20181202</t>
+          <t>20170506</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>07/03/2023</t>
+          <t>12/05/2019</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2023/02/05</t>
+          <t>2022/31/01</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>20250919</t>
+          <t>20210614</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>24/06/2016</t>
+          <t>27/06/2023</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>23-09-2025</t>
+          <t>22-02-2021</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>10/09/2020</t>
+          <t>06/03/2018</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2023/20/07</t>
+          <t>2022/17/10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2022/17/03</t>
+          <t>2024/27/04</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>19-10-2023</t>
+          <t>29-03-2023</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2016-17-12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>17/05/2020</t>
+          <t>25/04/2017</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024/05/01</t>
+          <t>2018/08/11</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2023/18/03</t>
+          <t>2025/15/10</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>24-06-2016</t>
+          <t>30-10-2020</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-21-08</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2019-16-09</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>20231211</t>
+          <t>20180817</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20180810</t>
+          <t>20240109</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>07-07-2021</t>
+          <t>06-09-2020</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2026-17-01</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>25/04/2019</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2024/03/11</t>
+          <t>2022/18/12</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>09-02-2024</t>
+          <t>25-04-2023</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>03/07/2017</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2018/10/08</t>
+          <t>2020/01/03</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>17-09-2019</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>20240319</t>
+          <t>20170224</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>17/01/2024</t>
+          <t>16/01/2021</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>10-11-2020</t>
+          <t>30-04-2017</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20220204</t>
+          <t>20250621</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>22/05/2023</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2016/24/06</t>
+          <t>2021/13/02</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>06-12-2022</t>
+          <t>15-01-2020</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2020-14-06</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20190917</t>
+          <t>20240817</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>12/01/2022</t>
+          <t>13/02/2023</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2023/03/12</t>
+          <t>2025/19/02</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2021-17-08</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20240224</t>
+          <t>20260409</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2019-19-09</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20170703</t>
+          <t>20250329</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>17-09-2019 08:56:36</t>
+          <t>25-06-2022 08:56:36</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>23-09-2023</t>
+          <t>26-05-2021</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20220916</t>
+          <t>20231004</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>20/12/2026</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>24-02-2022</t>
+          <t>28-03-2019</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2025-20-06</t>
+          <t>2023-20-06</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>07/05/2021</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>24/06/2016</t>
+          <t>07/10/2024</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>24-09-2022</t>
+          <t>05-06-2018</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2019-17-09</t>
+          <t>2021-14-01</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>20240329</t>
+          <t>20191216</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>15/05/2019</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2020/12/03</t>
+          <t>2017/21/06</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2022/10/12</t>
+          <t>2026/14/09</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>17-01-2023</t>
+          <t>14-02-2026</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2024-24-02</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2015/17/05</t>
+          <t>2018/20/10</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>19-07-2020</t>
+          <t>20-09-2017</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2020-20-01</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>20240615</t>
+          <t>20181221</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>29/10/2017</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>17/09/2019</t>
+          <t>25/08/2021</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2022/01/07</t>
+          <t>2020/26/07</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>20230117</t>
+          <t>20250429</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>30/03/2024</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>20220830</t>
+          <t>20170705</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20200828</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>03/07/2017</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2018/10/08</t>
+          <t>2021/20/04</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>05-04-2024</t>
+          <t>21-03-2020</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2024-25-12</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>20240515</t>
+          <t>20230207</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>15/06/2025</t>
+          <t>24/02/2021</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">

--- a/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
+++ b/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,12 +125,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2015/17/05</t>
+          <t>2021/10/09</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>07-08-2025</t>
+          <t>11-08-2020</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -172,12 +172,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -192,7 +192,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2022-22-07</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -234,12 +234,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -249,12 +249,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2018-20-04</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20230905</t>
+          <t>20170321</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -296,12 +296,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -316,7 +316,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16/03/2024</t>
+          <t>24/02/2021</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -358,12 +358,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023/05/04</t>
+          <t>2020/07/08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -420,12 +420,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -435,12 +435,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2020/24/10</t>
+          <t>2024/24/06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>01-01-2025</t>
+          <t>26-05-2023</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>krajoaw instytucja pieniądza elektronicznego</t>
+          <t>krajowa instytucja pieniądza elektronicznego</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>katywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2026-17-08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Worcław</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16/10/2017</t>
+          <t>10/08/2017</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2023/14/10</t>
+          <t>2022/27/08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13-05-2024</t>
+          <t>17-03-2024</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2023-24-01</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2015-17-05</t>
+          <t>2019-27-03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20230704</t>
+          <t>20180225</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20250217</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>03/07/2017</t>
+          <t>26/04/2022</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2018/10/08</t>
+          <t>2026/10/08</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mała instytucja pieniądza elektronicznego</t>
+          <t/>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20211103</t>
+          <t>20251120</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>21/10/2024</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2025/18/10</t>
+          <t>2017/14/12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2023/17/01</t>
+          <t>2026/20/07</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2025-20-09</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2236468458</t>
+          <t>1236468458</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27/12/2023</t>
+          <t>23/02/2017</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17/05/2015</t>
+          <t>25/04/2022</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025/09/02</t>
+          <t>2021/26/03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2022/25/08</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-23-05</t>
+          <t>2024-25-04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2018-10-08</t>
+          <t>2021-18-06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20190917</t>
+          <t>20250423</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Astra Finance SA</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2021/03/11</t>
+          <t>2026/08/02</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1247339575</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>27/09/2020</t>
+          <t>19/06/2018</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>24/06/2025</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>27-10-2024</t>
+          <t>14-12-2017</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1247577145</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2018-09-11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2016-24-06</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2019-12-10</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>12/09/2019</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>000000369</t>
+          <t>0000003694</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/08/2018</t>
+          <t>07/06/2020</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020/01/08</t>
+          <t>2019/09/05</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2019/17/09</t>
+          <t>2026/28/09</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23-12-2022</t>
+          <t>15-04-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20241018</t>
+          <t>20200130</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
+          <t>2018-09-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>02/02/2019</t>
+          <t>12/08/2018</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1248210665</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17/01/2023</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2024-22-12</t>
+          <t>2018-01-03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20200724</t>
+          <t>20171211</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2018-10-02</t>
+          <t>2018-02-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20150517</t>
+          <t>20191002</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>11/01/2018</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2025/25/01</t>
+          <t>2019/22/02</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1248685807</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2017/03/07</t>
+          <t>2025/11/05</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>25-08-2022</t>
+          <t>10-11-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2019-17-09</t>
+          <t>2024-28-11</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2024/09/10</t>
+          <t>2017/13/05</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12-04-2019</t>
+          <t>09-02-2018</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2018-21-11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Quantum eSrvices sp. z o. o.</t>
+          <t>Zielnoy Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>atkywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>17/05/2020</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2015/17/05</t>
+          <t>2018/03/07</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>06-01-2019</t>
+          <t>03-06-2017</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>24-06-2016</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>20250226</t>
+          <t>20240713</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2018-10-08 07:37</t>
+          <t>2025-08-10 07:37</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4078,12 +4078,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2024/16/01</t>
+          <t>2020/27/05</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2020/24/10</t>
+          <t>2026/25/08</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>03-11-2021</t>
+          <t>11-10-2025</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4388,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2019/23/07</t>
+          <t>2018/22/04</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Legionowo</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>08-12-2022</t>
+          <t>05-06-2022</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Marki</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2021-18-03</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4542,17 +4542,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2240427951</t>
+          <t>1240427951</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Otwock</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2015-17-05</t>
+          <t>2019-06-11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>20220126</t>
+          <t>20181007</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Radom</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>11/08/2020</t>
+          <t>16/12/2019</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Płock</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2024/03/10</t>
+          <t>2024/13/05</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -4760,12 +4760,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2024-29-05</t>
+          <t>2017-21-06</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Zakopane</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2020-24-10</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Mordarka</t>
         </is>
       </c>
     </row>
@@ -4946,17 +4946,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2019-02-07</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01/03/2019</t>
+          <t>08/01/2019</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Zielonki</t>
         </is>
       </c>
     </row>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2023/30/06</t>
+          <t>2018/13/01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Podłęże</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>08-02-2023</t>
+          <t>31-05-2021</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Tarnów</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>20180425</t>
+          <t/>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t/>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>17/05/2015</t>
+          <t>25/02/2023</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Zgierz</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2016/24/06</t>
+          <t>2018/03/02</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11-10-2020</t>
+          <t>04-01-2017</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -5442,12 +5442,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>20200329</t>
+          <t>20190123</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>000000844</t>
+          <t>0000008447</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Karpacz</t>
         </is>
       </c>
     </row>
@@ -5566,22 +5566,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20190917</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Lubin</t>
         </is>
       </c>
     </row>
@@ -5628,12 +5628,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Wałbrzych</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o. o.</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>12-01-2023</t>
+          <t>25-02-2018</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2017-12-08</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Helios Markets SP Z O O</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2023-17-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Kalisz</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Ostrów Wielkopolski</t>
         </is>
       </c>
     </row>
@@ -5938,12 +5938,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nova Data Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025/15/09</t>
+          <t>2023/14/12</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>27-11-2022</t>
+          <t>05-02-2017</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1252328545</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Polaris Capital SA</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>17-05-2015</t>
+          <t>11-01-2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2018-11-04</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Sopot</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Quantum Services S. A.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>20240618</t>
+          <t>20230213</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Chwaszczyno</t>
         </is>
       </c>
     </row>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2018-02-03</t>
+          <t>2018-03-02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>22/06/2025</t>
+          <t>04/01/2018</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -6248,12 +6248,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Gliwice</t>
         </is>
       </c>
     </row>
@@ -6372,12 +6372,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o. o.</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>19-12-2024</t>
+          <t>24-10-2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Helios Markets Sp. z o.o.</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>20181202</t>
+          <t>20170506</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Pruszków</t>
+          <t>Częstochowa</t>
         </is>
       </c>
     </row>
@@ -6496,17 +6496,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2019-11-06</t>
+          <t>2019-06-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>07/03/2023</t>
+          <t>12/05/2019</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Piaseczno</t>
+          <t>Bielsko-Biała</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2023/02/05</t>
+          <t>2022/31/01</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Wieliczka</t>
+          <t>Niechobrz</t>
         </is>
       </c>
     </row>
@@ -6620,12 +6620,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Oświęcim</t>
+          <t>Przemyśl</t>
         </is>
       </c>
     </row>
@@ -6682,12 +6682,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2017-06-10</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Krosno</t>
+          <t>Sanok</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>wydawca pieniądza elektroniczengo</t>
+          <t>wdyawca pieniądza elektronicznego</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Quantum Services SA</t>
+          <t>Niebieski Canyon SA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>akty</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>20250919</t>
+          <t>20210614</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Mielec</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -6806,17 +6806,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Silesia Invest S. A.</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Świdnica</t>
+          <t>Ogrodniczki</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka Akcyjna</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>24/06/2016</t>
+          <t>27/06/2023</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6898,17 +6898,17 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1253437207</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Hajnówka</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6930,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>23-09-2025</t>
+          <t>22-02-2021</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Gniezno</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -6992,12 +6992,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Leszno</t>
+          <t>Mięćmierz</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7054,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7084,17 +7084,17 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1253674775</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Tczew</t>
+          <t>Biała Podlaska</t>
         </is>
       </c>
     </row>
@@ -7116,17 +7116,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>wykreslony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2018-04-05</t>
+          <t>2018-05-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>10/09/2020</t>
+          <t>06/03/2018</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Wejherowo</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2023/20/07</t>
+          <t>2022/17/10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2022/17/03</t>
+          <t>2024/27/04</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>19-10-2023</t>
+          <t>29-03-2023</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Będzin</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -7302,12 +7302,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2016-17-12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Inowrocław</t>
+          <t>Mrągowo</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Grudziądz</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>17/05/2020</t>
+          <t>25/04/2017</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024/05/01</t>
+          <t>2018/08/11</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2023/18/03</t>
+          <t>2025/15/10</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Puławy</t>
+          <t>Kluczbork</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>24-06-2016</t>
+          <t>30-10-2020</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-21-08</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7642,17 +7642,17 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2244387450</t>
+          <t>1244387450</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Zamość</t>
+          <t>Gorzów Wielkopolski</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2019-16-09</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>20231211</t>
+          <t>20180817</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Międzyrzecz</t>
         </is>
       </c>
     </row>
@@ -7736,22 +7736,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20180810</t>
+          <t>20240109</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Suwałki</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7798,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Nysa</t>
+          <t>Busko-Zdrój</t>
         </is>
       </c>
     </row>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>07-07-2021</t>
+          <t>06-09-2020</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-01-08</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Żary</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -7984,12 +7984,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2026-17-01</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Świebodzin</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8046,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>25/04/2019</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Kołobrzeg</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -8108,12 +8108,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2024/03/11</t>
+          <t>2022/18/12</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Stargard</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Astra Finance S. A.</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>09-02-2024</t>
+          <t>25-04-2023</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Sandomierz</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Ostrowiec Świętokrzyski</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>03/07/2017</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2018/10/08</t>
+          <t>2020/01/03</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>17-09-2019</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>000001320</t>
+          <t>0000013200</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8619,12 +8619,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>20240319</t>
+          <t>20170224</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Biała Podlaska</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8666,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>17/01/2024</t>
+          <t>16/01/2021</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -8728,12 +8728,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>10-11-2020</t>
+          <t>30-04-2017</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -8852,12 +8852,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -8976,12 +8976,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20220204</t>
+          <t>20250621</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9011,12 +9011,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>22/05/2023</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9068,17 +9068,17 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1256208855</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -9100,12 +9100,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2016/24/06</t>
+          <t>2021/13/02</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>06-12-2022</t>
+          <t>15-01-2020</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2020-14-06</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9259,12 +9259,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20190917</t>
+          <t>20240817</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9321,12 +9321,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -9348,12 +9348,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>12/01/2022</t>
+          <t>13/02/2023</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2023/03/12</t>
+          <t>2025/19/02</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>30-12-2025</t>
+          <t/>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2021-17-08</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -9534,12 +9534,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -9596,22 +9596,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20240224</t>
+          <t>20260409</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -9782,12 +9782,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2019-19-09</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>wydawca pieniądza elektronicznego</t>
+          <t>wydawca pieniądza elektroniczneog</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Quantum Serviecs Sp. z o.o.</t>
+          <t>Amber Doradztwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>wyrk</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -9906,12 +9906,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20170703</t>
+          <t>20250329</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9936,17 +9936,17 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1257317517</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -9968,12 +9968,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>17-09-2019 08:56:36</t>
+          <t>25-06-2022 08:56:36</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>23-09-2023</t>
+          <t>26-05-2021</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1257555085</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Pruszków</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Piaseczno</t>
         </is>
       </c>
     </row>
@@ -10216,22 +10216,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20220916</t>
+          <t>20231004</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Wieliczka</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>20/12/2026</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10308,17 +10308,17 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>2257792655</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Oświęcim</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10340,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>24-02-2022</t>
+          <t>28-03-2019</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Krosno</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2025-20-06</t>
+          <t>2023-20-06</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Mielec</t>
         </is>
       </c>
     </row>
@@ -10464,12 +10464,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Świdnica</t>
         </is>
       </c>
     </row>
@@ -10526,12 +10526,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>07/05/2021</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Pruszków</t>
+          <t>Kłodzko</t>
         </is>
       </c>
     </row>
@@ -10588,12 +10588,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>24/06/2016</t>
+          <t>07/10/2024</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Piaseczno</t>
+          <t>Gniezno</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Astra Finance spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>24-09-2022</t>
+          <t>05-06-2018</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Wieliczka</t>
+          <t>Leszno</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10712,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10742,17 +10742,17 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2248346956</t>
+          <t>1248346956</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Oświęcim</t>
+          <t>Tczew</t>
         </is>
       </c>
     </row>
@@ -10774,12 +10774,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2019-17-09</t>
+          <t>2021-14-01</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>20240329</t>
+          <t>20191216</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Krosno</t>
+          <t>Wejherowo</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>15/05/2019</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Mielec</t>
+          <t>Cieszyn</t>
         </is>
       </c>
     </row>
@@ -10898,12 +10898,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2020/12/03</t>
+          <t>2017/21/06</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Świdnica</t>
+          <t>Będzin</t>
         </is>
       </c>
     </row>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2022/10/12</t>
+          <t>2026/14/09</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Inowrocław</t>
         </is>
       </c>
     </row>
@@ -11022,12 +11022,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>17-01-2023</t>
+          <t>14-02-2026</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Gniezno</t>
+          <t>Grudziądz</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2024-24-02</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Leszno</t>
+          <t>Ostróda</t>
         </is>
       </c>
     </row>
@@ -11146,17 +11146,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -11181,12 +11181,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Tczew</t>
+          <t>Giżycko</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Wejherowo</t>
+          <t>Puławy</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11270,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2015/17/05</t>
+          <t>2018/20/10</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>19-07-2020</t>
+          <t>20-09-2017</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Zamość</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11332,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Będzin</t>
+          <t>Augustów</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11394,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2017-03-07</t>
+          <t>2020-20-01</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>20240615</t>
+          <t>20181221</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11429,12 +11429,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Inowrocław</t>
+          <t>Suwałki</t>
         </is>
       </c>
     </row>
@@ -11456,12 +11456,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>29/10/2017</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11518,12 +11518,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>17/09/2019</t>
+          <t>25/08/2021</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2022/01/07</t>
+          <t>2020/26/07</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11553,12 +11553,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Ostróda</t>
+          <t>Brzeg</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>000001795</t>
+          <t>0000017953</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Giżycko</t>
+          <t>Żary</t>
         </is>
       </c>
     </row>
@@ -11642,12 +11642,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2019-02-09</t>
+          <t>2019-09-02</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Puławy</t>
+          <t>Świebodzin</t>
         </is>
       </c>
     </row>
@@ -11704,12 +11704,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Zamość</t>
+          <t>Kołobrzeg</t>
         </is>
       </c>
     </row>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>20230117</t>
+          <t>20250429</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>30/03/2024</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Stargard</t>
         </is>
       </c>
     </row>
@@ -11828,12 +11828,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Suwałki</t>
+          <t>Sandomierz</t>
         </is>
       </c>
     </row>
@@ -11890,12 +11890,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Astra Finance Sp. z o.o.</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Nysa</t>
+          <t>Ostrowiec Świętokrzyski</t>
         </is>
       </c>
     </row>
@@ -11952,12 +11952,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2020-10-11</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>0000018535</t>
+          <t>000001853</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -12014,12 +12014,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>20220830</t>
+          <t>20170705</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Żary</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -12076,12 +12076,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>20160624</t>
+          <t>20200828</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Świebodzin</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12138,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>03/07/2017</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12173,12 +12173,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Kołobrzeg</t>
+          <t>Legionowo</t>
         </is>
       </c>
     </row>
@@ -12200,12 +12200,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2018/10/08</t>
+          <t>2021/20/04</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>05-04-2024</t>
+          <t>21-03-2020</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12235,12 +12235,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Stargard</t>
+          <t>Marki</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2024-25-12</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Sandomierz</t>
+          <t>Otwock</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>20240515</t>
+          <t>20230207</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12359,12 +12359,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Ostrowiec Świętokrzyski</t>
+          <t>Radom</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>15/06/2025</t>
+          <t>24/02/2021</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Płock</t>
         </is>
       </c>
     </row>
@@ -12448,12 +12448,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
+++ b/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
@@ -110,7 +110,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Facebook - Meta</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -135,22 +135,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0000000008</t>
+          <t>0000058208</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1234805466</t>
+          <t>1282319462</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
+          <t>ul. Zwycięstwa 121/61, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Gliwice</t>
         </is>
       </c>
     </row>
@@ -172,7 +172,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Polskie Przetwory sp z oo</t>
+          <t>Zielony Bieszczady S.A.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -197,22 +197,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0000000105</t>
+          <t>0000058305</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1234884655</t>
+          <t>1282398651</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
+          <t>ul Bocheńskiego 138, 43-100 Tychy</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Tychy</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
+          <t>Zielony Karpaty SA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -259,22 +259,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0000000202</t>
+          <t>0000058402</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1234963840</t>
+          <t>1282477847</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ulica Floriańska 35, 31-019 Kraków</t>
+          <t>ulica Najświętszej Maryi Panny 155, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Częstochowa</t>
         </is>
       </c>
     </row>
@@ -296,7 +296,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
+          <t>Zielony Bałtyk S. A.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -321,22 +321,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0000000299</t>
+          <t>0000058499</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1235043030</t>
+          <t>1282557032</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Długa 52, 31-147 Kraków</t>
+          <t>11 Listopada 172, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Bielsko-Biała</t>
         </is>
       </c>
     </row>
@@ -358,7 +358,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kancelaria Prawna Sankcja SP Z O O</t>
+          <t>Zielony Sudety Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -383,22 +383,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0000000396</t>
+          <t>0000058596</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1235122226</t>
+          <t>1282636228</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
+          <t>9/23, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Niechobrz</t>
         </is>
       </c>
     </row>
@@ -420,7 +420,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -445,22 +445,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0000000493</t>
+          <t>0000058693</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1235201411</t>
+          <t>1282715413</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ul Zachodnia 86, 90-402 Łódź</t>
+          <t>ul Franciszkańska 26, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Przemyśl</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Bizon sp z oo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -507,22 +507,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0000000590</t>
+          <t>0000058790</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1235280600</t>
+          <t>1282794602</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
+          <t>ulica Kościuszki 43, 38-500 Sanok</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Sanok</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UKNF-EPI-4290/2025</t>
+          <t>UKFN-EPI-4290/2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
+          <t>Niebieski Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -569,22 +569,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0000000687</t>
+          <t>0000058887</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1235359796</t>
+          <t>1282873796</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Legnicka 120, 54-203 Wrocław</t>
+          <t>Suraska 60, 15-422 Białystok</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Worcław</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Krakowskie Biuro Nieruchomości SA</t>
+          <t>Niebieski Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0000000784</t>
+          <t>0000058984</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1235438981</t>
+          <t>1282952981</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
+          <t>77/75, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Ogrodniczki</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Salon Samochodowy Auto-Hit S. A.</t>
+          <t>Niebieski Echo SP Z O O</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0000000881</t>
+          <t>0000059081</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1235518177</t>
+          <t>1283032171</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ul Głogowska 154, 60-734 Poznań</t>
+          <t>os. 3 Maja 94, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Hajnówka</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
+          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0000000978</t>
+          <t>0000059178</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1235597366</t>
+          <t>1283111367</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ulica Długa 171, 80-831 Gdańsk</t>
+          <t>ulica os. LSM 111, 20-400 Lublin</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Polski Tytoń sp. z o.o.</t>
+          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -812,27 +812,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2017-05-10</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0000001075</t>
+          <t>0000059275</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1235676551</t>
+          <t>1283190556</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
+          <t>128, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Mięćmierz</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gdańska Stocznia Jachtowa sp z oo</t>
+          <t>Niebieski Horyzont S.A.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -879,22 +879,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0000001172</t>
+          <t>0000059372</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1235755747</t>
+          <t>1283269743</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
+          <t>ul. Brzeska 145/37, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Biała Podlaska</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
+          <t>Niebieski Ikar SA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0000001269</t>
+          <t>0000059469</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1235834932</t>
+          <t>1283348939</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
+          <t>ul Rynek Staromiejski 162, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
+          <t>Niebieski Jantar S. A.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0000001366</t>
+          <t>0000059566</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1235914128</t>
+          <t>1283428124</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ulica Mariacka 59, 40-014 Katowice</t>
+          <t>ulica Mostowa 179, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
+          <t>Niebieski Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0000001463</t>
+          <t>0000059663</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1235993317</t>
+          <t>1293507345</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Warszawska 76, 40-009 Katowice</t>
+          <t>Stare Miasto 16, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0000001560</t>
+          <t>0000059760</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1236072507</t>
+          <t>1283586509</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
+          <t>ul. Warszawska 33/89, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Mrągowo</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Magnolia sp z oo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1189,22 +1189,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0000001657</t>
+          <t>0000059857</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1236151690</t>
+          <t>1283665692</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
+          <t>ul Wojska Polskiego 50, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Polskie Linie Oceaniczne S.A.</t>
+          <t>Niebieski Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0000001754</t>
+          <t>0000059954</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1236230886</t>
+          <t>1283744888</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ulica Lipowa 127, 15-424 Białystok</t>
+          <t>ulica Monte Cassino 67, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Świnoujście</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
+          <t>Niebieski Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0000001851</t>
+          <t>0000060051</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1236310071</t>
+          <t>1283824073</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PPHU Studio Projektowe Architektura</t>
+          <t>P.P.H.U. Niebieski Pegaz</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1375,22 +1375,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0000001948</t>
+          <t>0000060148</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1236389262</t>
+          <t>1283903269</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
+          <t>ul. Byczyńska 101/51, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Kluczbork</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
+          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1432,27 +1432,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0000002045</t>
+          <t>0000060245</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1236468458</t>
+          <t>1283982458</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
+          <t>ul Chrobrego 118, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Gorzów Wielkopolski</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
+          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0000002142</t>
+          <t>0000060342</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1236547643</t>
+          <t>1284061648</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ulica Szeroka 15, 87-100 Toruń</t>
+          <t>ulica 30 Stycznia 135, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Międzyrzecz</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
+          <t>Niebieski Tytan S.A.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1561,22 +1561,22 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0000002239</t>
+          <t>0000060439</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1236626839</t>
+          <t>1284140833</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Chełmińska 32, 87-100 Toruń</t>
+          <t>Paderewskiego 152, 25-004 Kielce</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
+          <t>Niebieski Uran SA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1623,22 +1623,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0000002336</t>
+          <t>0000060536</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1236706024</t>
+          <t>1284220029</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
+          <t>ul. 1 Maja 169/13, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Busko-Zdrój</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
+          <t>Niebieski Wektor S. A.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0000002433</t>
+          <t>0000060633</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1236785213</t>
+          <t>1294299245</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
+          <t>ul Marszałkowska 6, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polska Grupa Energetyczna SP Z O O</t>
+          <t>Niebieski Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1747,22 +1747,22 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0000002530</t>
+          <t>0000060730</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1236864409</t>
+          <t>1284378405</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
+          <t>ulica Krakowskie Przedmieście 23, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1809,22 +1809,22 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0000002627</t>
+          <t>0000060827</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1236943592</t>
+          <t>1284457599</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Warszawska 100, 25-512 Kielce</t>
+          <t>Floriańska 40, 31-019 Kraków</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Sokół sp z oo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0000002724</t>
+          <t>0000060924</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1237022782</t>
+          <t>1284536784</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
+          <t>ul. Długa 57/65, 31-147 Kraków</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kancelaria Notarialna Lex S.A.</t>
+          <t>Niebieski Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0000002821</t>
+          <t>0000061021</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1237101978</t>
+          <t>1294616007</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
+          <t>ul Piotrkowska 74, 90-102 Łódź</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Biuro Podróży Wojażer SA</t>
+          <t>Niebieski Kormoran Sp. z o.o.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1995,22 +1995,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0000002918</t>
+          <t>0000061118</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1237181167</t>
+          <t>1284695169</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ulica Krakowska 151, 45-018 Opole</t>
+          <t>ulica Zachodnia 91, 90-402 Łódź</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Szkoła Języków Obcych Lingua S. A.</t>
+          <t>Niebieski Barycz SP Z O O</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2057,22 +2057,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0000003015</t>
+          <t>0000061215</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1237260352</t>
+          <t>1284774354</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ozimska 168, 45-057 Opole</t>
+          <t>Świdnicka 108, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
+          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0000003112</t>
+          <t>0000061312</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1247339575</t>
+          <t>1294853575</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 5/57, 65-034 Zielona Góra</t>
+          <t>ul. Legnicka 125/27, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
+          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0000003209</t>
+          <t>0000061409</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1284932735</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>ul Kupiecka 22, 65-058 Zielona Góra</t>
+          <t>ul Święty Marcin 142, 61-806 Poznań</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Polskie Sady sp z oo</t>
+          <t>Niebieski Narew S.A.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0000003306</t>
+          <t>0000061506</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1237497924</t>
+          <t>1285011925</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 39, 81-372 Gdynia</t>
+          <t>ulica Głogowska 159, 60-734 Poznań</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
+          <t>Niebieski Jodełka SA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0000003403</t>
+          <t>0000061603</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1247577145</t>
+          <t>1285091114</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10 Lutego 56, 81-364 Gdynia</t>
+          <t>Długa 176, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
+          <t>Niebieski Kaktus S. A.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2362,27 +2362,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2018-09-11</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0000003500</t>
+          <t>0000061700</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1295170335</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 73/19, 05-800 Pruszków</t>
+          <t>ul. Grunwaldzka 13/79, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Pruszków</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
+          <t>Niebieski Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0000003597</t>
+          <t>0000061797</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1237735499</t>
+          <t>1285249495</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2019-12-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0000003694</t>
+          <t>0000061894</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1237814684</t>
+          <t>1285328680</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 107, 32-020 Wieliczka</t>
+          <t>os. Wyszyńskiego 47, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Wieliczka</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Granit sp z oo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2553,22 +2553,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0000003791</t>
+          <t>0000061991</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1237893873</t>
+          <t>1285407876</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 124, 32-600 Oświęcim</t>
+          <t>Mariacka 64, 40-014 Katowice</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Oświęcim</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Instagram - Meta</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2615,22 +2615,22 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0000003888</t>
+          <t>0000062088</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1237973069</t>
+          <t>1285487065</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ul. Rynek 141/71, 38-400 Krosno</t>
+          <t>ul. Warszawska 81/41, 40-009 Katowice</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Krosno</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Krajowa Izba Gospodarcza SA</t>
+          <t>Niebieski Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2677,22 +2677,22 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0000003985</t>
+          <t>0000062185</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1238052259</t>
+          <t>1285566250</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 158, 39-300 Mielec</t>
+          <t>ul Krakowskie Przedmieście 98, 20-002 Lublin</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Mielec</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Polskie Zakłady Lotnicze S. A.</t>
+          <t>Niebieski Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0000004082</t>
+          <t>0000062282</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1238131444</t>
+          <t>1285645446</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>175, 58-100 Świdnica</t>
+          <t>ulica Narutowicza 115, 20-004 Lublin</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Świdnica</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
+          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2018-09-11</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2801,22 +2801,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0000004179</t>
+          <t>0000062379</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1248210665</t>
+          <t>1285724631</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Wojska Polskiego 12, 57-300 Kłodzko</t>
+          <t>Lipowa 132, 15-424 Białystok</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
+          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2863,22 +2863,22 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0000004276</t>
+          <t>0000062476</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1285803827</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 29/33, 62-200 Gniezno</t>
+          <t>ul. Sienkiewicza 149/3, 15-092 Białystok</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Gniezno</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
+          <t>Niebieski Krokus S.A.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0000004373</t>
+          <t>0000062573</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1238369016</t>
+          <t>1285883016</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>ul Słowiańska 46, 64-100 Leszno</t>
+          <t>ul Gdańska 166, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Leszno</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zakład Usług Komunalnych sp. z o. o.</t>
+          <t>Niebieski Narcyz SA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2982,27 +2982,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0000004470</t>
+          <t>0000062670</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1238448201</t>
+          <t>1285962201</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>ulica Gdańska 63, 83-110 Tczew</t>
+          <t>ulica Dworcowa 3, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Tczew</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Polski Komfort Sp. z o.o.</t>
+          <t>Niebieski Giewont S. A.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3049,22 +3049,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0000004567</t>
+          <t>0000062767</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1238527395</t>
+          <t>1296041427</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Sobieskiego 80, 84-200 Wejherowo</t>
+          <t>Szeroka 20, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Wejherowo</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
+          <t>Niebieski Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2018-02-10</t>
+          <t>2018-10-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3111,22 +3111,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0000004664</t>
+          <t>0000062864</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1238606580</t>
+          <t>1286120585</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>ul. Głęboka 97/85, 43-400 Cieszyn</t>
+          <t>ul. Chełmińska 37/55, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3173,22 +3173,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0000004761</t>
+          <t>0000062961</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1248685807</t>
+          <t>1286199776</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>114, 42-500 Będzin</t>
+          <t>ul 3 Maja 54, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Będzin</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Budownictwo sp z oo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3235,22 +3235,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0000004858</t>
+          <t>0000063058</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1286278961</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 131, 88-100 Inowrocław</t>
+          <t>ulica Piłsudskiego 71, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Inowrocław</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fabryka Tekstyliów Splot S.A.</t>
+          <t>Amber Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3292,27 +3292,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0000004955</t>
+          <t>0000063155</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1238844150</t>
+          <t>1286358157</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Wybickiego 148, 86-300 Grudziądz</t>
+          <t>Sienkiewicza 88, 25-007 Kielce</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Grudziądz</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Górnośląskie Towarzystwo Finansowe SA</t>
+          <t>Amber Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3359,22 +3359,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0000005052</t>
+          <t>0000063252</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1238923346</t>
+          <t>1286437342</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 165/47, 14-100 Ostróda</t>
+          <t>ul. Warszawska 105/17, 25-512 Kielce</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Ostróda</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Krajowa Agencja Informacyjna S. A.</t>
+          <t>Amber Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0000005149</t>
+          <t>0000063349</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1239002536</t>
+          <t>1286516538</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ul Warszawska 2, 11-500 Giżycko</t>
+          <t>ul Kościuszki 122, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Giżycko</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Polskie Jagody Spółka Akcyjna</t>
+          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3483,22 +3483,22 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0000005246</t>
+          <t>0000063446</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1239081725</t>
+          <t>1286595727</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>ulica Lubelska 19, 24-100 Puławy</t>
+          <t>ulica Dąbrowszczaków 139, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Puławy</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Zielony Amber sp. z o.o.</t>
+          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0000005343</t>
+          <t>0000063543</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1239160910</t>
+          <t>1286674912</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Staszica 36, 22-400 Zamość</t>
+          <t>Krakowska 156, 45-018 Opole</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Zamość</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Zielony Bizon sp z oo</t>
+          <t>Amber Finanse S.A.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3607,22 +3607,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0000005440</t>
+          <t>0000063640</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1239240106</t>
+          <t>1286754108</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>53/9, 16-300 Augustów</t>
+          <t>ul. Ozimska 173/69, 45-057 Opole</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Zielnoy Canyon sp. z o. o.</t>
+          <t>Amber Doradztwo SA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3669,22 +3669,22 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0000005537</t>
+          <t>0000063737</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1239319291</t>
+          <t>1286833291</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>ul Kościuszki 70, 16-400 Suwałki</t>
+          <t>ul Bohaterów Westerplatte 10, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Suwałki</t>
+          <t>Zileona Góra</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Zielony Delfin Sp. z o.o.</t>
+          <t>Amber Szkolenia S. A.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3731,22 +3731,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0000005634</t>
+          <t>0000063834</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1239398480</t>
+          <t>1286912487</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>os. Piastowska 87, 48-300 Nysa</t>
+          <t>ulica Kupiecka 27, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Nysa</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Zielony Echo SP Z O O</t>
+          <t>Amber Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3793,22 +3793,22 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0000005731</t>
+          <t>0000063931</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1239477676</t>
+          <t>1286991676</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Długa 104, 49-300 Brzeg</t>
+          <t>Świętojańska 44, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Zielony Falcon</t>
+          <t>PPHU Amber Reklama</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0000005828</t>
+          <t>0000064028</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1239556861</t>
+          <t>1287070866</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>ul. Rynek 121/61, 68-200 Żary</t>
+          <t>ul. 10 Lutego 61/31, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Żary</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Marketing sp z oo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0000005925</t>
+          <t>0000064125</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1239636057</t>
+          <t>1287150051</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 138, 66-200 Świebodzin</t>
+          <t>ul Bolesława Prusa 78, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Świebodzin</t>
+          <t>Pruszków</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Zielony Horyzont S.A.</t>
+          <t>Amber Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3979,22 +3979,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0000006022</t>
+          <t>0000064222</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1239715242</t>
+          <t>1287229249</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 155, 78-100 Kołobrzeg</t>
+          <t>ulica Kościuszki 95, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Kołobrzeg</t>
+          <t>Piaseczno</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Zielony Ikar SA</t>
+          <t>Amber Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4041,22 +4041,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0000006119</t>
+          <t>0000064319</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1239794431</t>
+          <t>1287308434</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Piłsudskiego 172, 73-110 Stargard</t>
+          <t>Sienkiewicza 112, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Stargard</t>
+          <t>Wieliczka</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Zielony Jantar S. A.</t>
+          <t>Amber Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4103,22 +4103,22 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0000006216</t>
+          <t>0000064416</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1239873627</t>
+          <t>1287387623</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ul. Mickiewicza 9/23, 27-600 Sandomierz</t>
+          <t>ul. Dąbrowskiego 129/83, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Sandomierz</t>
+          <t>Oświęcim</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Zielony Koral Spółka Akcyjna</t>
+          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0000006313</t>
+          <t>0000064513</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1239952812</t>
+          <t>1287466819</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 26, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>146, 38-400 Krosno</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Ostrowiec Świętokrzyski</t>
+          <t>Krosno</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Zielony Lotos sp. z o.o.</t>
+          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4227,22 +4227,22 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0000006410</t>
+          <t>0000064610</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1240032000</t>
+          <t>1287546004</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ulica Chmielna 43, 00-020 Warszawa</t>
+          <t>ulica Mickiewicza 163, 39-300 Mielec</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Mielec</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Zielony Magnolia sp z oo</t>
+          <t>Amber Produkcja S.A.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4289,22 +4289,22 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0000006507</t>
+          <t>0000064707</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1240111194</t>
+          <t>1287625198</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Nowy Świat 60, 00-029 Warszawa</t>
+          <t>os. Długa 180, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Świdnica</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Zielony Neon sp. z o. o.</t>
+          <t>Amber Przemysł SA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4351,22 +4351,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0000006604</t>
+          <t>0000064804</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1240190383</t>
+          <t>1287704383</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
+          <t>ul. Wojska Polskiego 17/45, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Kłodzko</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Zielony Oaza Sp. z o.o.</t>
+          <t>Amber Ekologia S. A.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4413,22 +4413,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0000006701</t>
+          <t>0000064901</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1240269570</t>
+          <t>1287783572</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
+          <t>ul Chrobrego 34, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Legionowo</t>
+          <t>Gniezno</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Zielony Pegaz SP Z O O</t>
+          <t>Amber Energetyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0000006798</t>
+          <t>0000064998</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1240348766</t>
+          <t>1287862768</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
+          <t>ulica Słowiańska 51, 64-100 Leszno</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Marki</t>
+          <t>Leszno</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4532,27 +4532,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0000006895</t>
+          <t>0000065095</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1240427951</t>
+          <t>1287941953</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Andriollego 128, 05-400 Otwock</t>
+          <t>Gdańska 68, 83-110 Tczew</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Otwock</t>
+          <t>Tczew</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
+          <t>2019-11-06</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4599,22 +4599,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0000006992</t>
+          <t>0000065192</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1240507147</t>
+          <t>1288021143</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
+          <t>85/7, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Radom</t>
+          <t>Wejherowo</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Zielony Tytan S.A.</t>
+          <t>Amber Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4661,22 +4661,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0000007089</t>
+          <t>0000065289</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1240586336</t>
+          <t>1288100339</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ul Tumska 162, 09-402 Płock</t>
+          <t>ul Głęboka 102, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Płock</t>
+          <t>Cieszyn</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Zielony Uran SA</t>
+          <t>Amber Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4723,22 +4723,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0000007186</t>
+          <t>0000065386</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1240665521</t>
+          <t>1298179555</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ulica Karmelicka 179, 31-128 Kraków</t>
+          <t>ulica Małachowskiego 119, 42-500 Będzin</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Będzin</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Zielony Wektor S. A.</t>
+          <t>Amber Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4785,22 +4785,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0000007283</t>
+          <t>0000065483</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1240744717</t>
+          <t>1288258715</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>os. Na Stoku 16, 31-704 Kraków</t>
+          <t>Królowej Jadwigi 136, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Inowrocław</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Zielony Zefir Spółka Akcyjna</t>
+          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0000007380</t>
+          <t>0000065580</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1240823902</t>
+          <t>1288337900</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
+          <t>ul. Wybickiego 153/59, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Zakopane</t>
+          <t>Grudziądz</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Zielony Żubr sp. z o.o.</t>
+          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4909,22 +4909,22 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0000007477</t>
+          <t>0000065677</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1240903096</t>
+          <t>1288417094</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>50, 34-600 Mordarka</t>
+          <t>ul Czarnieckiego 170, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Mordarka</t>
+          <t>Ostróda</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Zielony Sokół sp z oo</t>
+          <t>Amber Rozrywka S.A.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2019-07-02</t>
+          <t>2019-02-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4971,22 +4971,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0000007574</t>
+          <t>0000065774</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1240982285</t>
+          <t>1288496283</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
+          <t>ulica Warszawska 7, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Zielonki</t>
+          <t>Giżycko</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Zielony Orzeł sp. z o. o.</t>
+          <t>Amber Gastronomia SA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5033,22 +5033,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0000007671</t>
+          <t>0000065871</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1241061475</t>
+          <t>1288575479</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>84, 32-003 Podłęże</t>
+          <t>24, 24-100 Puławy</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Podłęże</t>
+          <t>Puławy</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>mBank</t>
+          <t>Instagram - Meta</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0000007768</t>
+          <t>0000065968</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1241140660</t>
+          <t>1288654664</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
+          <t>ul. Staszica 41/21, 22-400 Zamość</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Tarnów</t>
+          <t>Zamość</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Zielony Barycz SP Z O O</t>
+          <t>Amber Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0000007865</t>
+          <t>0000066065</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1241219858</t>
+          <t>1298733885</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>ul Narutowicza 118, 90-135 Łódź</t>
+          <t>ul 3 Maja 58, 16-300 Augustów</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Augustów</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0000007962</t>
+          <t>0000066162</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1241299047</t>
+          <t>1288813045</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Suwałki</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0000008059</t>
+          <t>0000066259</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>1241378232</t>
+          <t>1288892234</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Zielony Narew S.A.</t>
+          <t>Amber Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5343,22 +5343,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0000008156</t>
+          <t>0000066356</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1241457428</t>
+          <t>1298971455</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>ul. Długa 169/13, 95-100 Zgierz</t>
+          <t>ul. Długa 109/73, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Zgierz</t>
+          <t>Brzeg</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Zielony Jodełka SA</t>
+          <t>Amber Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5405,22 +5405,22 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0000008253</t>
+          <t>0000066453</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1241536613</t>
+          <t>1299050645</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>ul Rynek 6, 50-101 Wrocław</t>
+          <t>ul Rynek 126, 68-200 Żary</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Żary</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Zielony Kaktus S. A.</t>
+          <t>Amber Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5467,22 +5467,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0000008350</t>
+          <t>0000066550</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1241615809</t>
+          <t/>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
+          <t>143, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Świebodzin</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Zielony Szmaragd Spółka Akcyjna</t>
+          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5529,22 +5529,22 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0000008447</t>
+          <t>0000066647</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1241694996</t>
+          <t>1289208990</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
+          <t>Armii Krajowej 160, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Karpacz</t>
+          <t>Kołobrzeg</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Zielony Topaz sp. z o.o.</t>
+          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5591,22 +5591,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0000008544</t>
+          <t>0000066744</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t/>
+          <t>1299288217</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
+          <t>ul. Piłsudskiego 177/35, 73-110 Stargard</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Lubin</t>
+          <t>Stargard</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Zielony Granit sp z oo</t>
+          <t>Amber Księgowość S.A.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5653,22 +5653,22 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0000008641</t>
+          <t>0000066841</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1241853377</t>
+          <t>1289367375</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
+          <t>ul Mickiewicza 14, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Wałbrzych</t>
+          <t>Sandomierz</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Zielony Marmur sp. z o. o.</t>
+          <t>Bizon Budownictwo SA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5715,22 +5715,22 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0000008738</t>
+          <t>0000066938</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1241932562</t>
+          <t>1289446560</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>ulica Półwiejska 91, 61-888 Poznań</t>
+          <t>ulica Sienkiewicza 31, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Ostrowiec Świętokrzyski</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Zielony Syrena Sp. z o.o.</t>
+          <t>Bizon Transport S. A.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5772,27 +5772,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2017-12-08</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>0000008835</t>
+          <t>0000067035</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1242011752</t>
+          <t>1289525756</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
+          <t>Chmielna 48, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Zielony Zodiak SP Z O O</t>
+          <t>Bizon Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5839,22 +5839,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>0000008932</t>
+          <t>0000067132</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1242090941</t>
+          <t>1289604941</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
+          <t>ul. Nowy Świat 65/87, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Kalisz</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5901,22 +5901,22 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>0000009029</t>
+          <t>0000067229</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1242170137</t>
+          <t>1289684130</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
+          <t>ul os. Przyjaźń 82, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ostrów Wielkopolski</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Handel sp z oo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5963,22 +5963,22 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0000009126</t>
+          <t>0000067326</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1242249324</t>
+          <t>1289763326</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
+          <t>ulica Jagiellońska 99, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Legionowo</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Zielony Krokus S.A.</t>
+          <t>Bizon Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6025,22 +6025,22 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0000009223</t>
+          <t>0000067423</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1252328545</t>
+          <t>1289842511</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>os. Jasień 176, 80-180 Gdańsk</t>
+          <t>Piłsudskiego 116, 05-270 Marki</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Marki</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Zielony Narcyz SA</t>
+          <t>Bizon Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6082,27 +6082,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>0000009320</t>
+          <t>0000067520</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1289921707</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
+          <t>os. Andriollego 133/49, 05-400 Otwock</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sopot</t>
+          <t>Otwock</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Zielony Giewont S. A.</t>
+          <t>Bizon Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6149,22 +6149,22 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>0000009417</t>
+          <t>0000067617</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1242486892</t>
+          <t>1290000893</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>30, 80-209 Chwaszczyno</t>
+          <t>ul Żeromskiego 150, 26-600 Radom</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Chwaszczyno</t>
+          <t>Radom</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Zielony Rysy Spółka Akcyjna</t>
+          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2018-03-02</t>
+          <t>2018-02-03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6211,22 +6211,22 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>0000009514</t>
+          <t>0000067714</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>1242566088</t>
+          <t>1290080082</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 47, 40-096 Katowice</t>
+          <t>ulica Tumska 167, 09-402 Płock</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Płock</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Zielony Kasprowy sp. z o.o.</t>
+          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>0000009611</t>
+          <t>0000067811</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1242645273</t>
+          <t>1300159308</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>os. Paderewskiego 64, 40-282 Katowice</t>
+          <t>Karmelicka 4, 31-128 Kraków</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PPHU Zielony Beskid</t>
+          <t>P.P.H.U. Bizon Reklama</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6335,22 +6335,22 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>0000009708</t>
+          <t>0000067908</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>1242724469</t>
+          <t>1290238465</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
+          <t>ul. os. Na Stoku 21/11, 31-704 Kraków</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Gliwice</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady sp. z o. o.</t>
+          <t>Bizon Marketing SA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>0000009805</t>
+          <t>0000068005</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>1242803654</t>
+          <t>1290317650</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Zielony Karpaty Sp. z o.o.</t>
+          <t>Bizon Druk S. A.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6459,22 +6459,22 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>0000009902</t>
+          <t>0000068102</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1242882843</t>
+          <t>1300396876</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
+          <t>55, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Częstochowa</t>
+          <t>Mordarka</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk SP Z O O</t>
+          <t>Bizon Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
+          <t>2019-11-06</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>0000009999</t>
+          <t>0000068199</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1242962039</t>
+          <t>1290476035</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
+          <t>Galicyjska 72, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Bielsko-Biała</t>
+          <t>Zielonki</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6583,22 +6583,22 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0000010096</t>
+          <t>0000068296</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>1243041229</t>
+          <t>1290555220</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>149/3, 36-047 Niechobrz</t>
+          <t>89/63, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Niechobrz</t>
+          <t>Podłęże</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6645,22 +6645,22 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0000010193</t>
+          <t>0000068393</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>1243120414</t>
+          <t>1290634416</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
+          <t>ul Wałowa 106, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Przemyśl</t>
+          <t>Tarnów</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Niebieski Bizon S.A.</t>
+          <t>Bizon Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6702,27 +6702,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2017-06-10</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>0000010290</t>
+          <t>0000068490</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>1243199605</t>
+          <t>1290713601</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 3, 38-500 Sanok</t>
+          <t>ulica Narutowicza 123, 90-135 Łódź</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Sanok</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UKNF-EPI-5232/2020</t>
+          <t>UNKF-EPI-5232/2020</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Niebieski Canyon SA</t>
+          <t>Bizon Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6769,22 +6769,22 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>0000010387</t>
+          <t>0000068587</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1243278799</t>
+          <t>1290792799</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Suraska 20, 15-422 Białystok</t>
+          <t>os. Retkinia 140, 94-004 Łódź</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Niebieski Delfin S. A.</t>
+          <t>Bizon Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>0000010484</t>
+          <t>0000068684</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1243357984</t>
+          <t>1290871984</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>37/55, 16-030 Ogrodniczki</t>
+          <t>ul. Zamkowa 157/25, 95-200 Pabianice</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Ogrodniczki</t>
+          <t>Pabianice</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Niebieski Echo Spółka Akcyjna</t>
+          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6893,22 +6893,22 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>0000010581</t>
+          <t>0000068781</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1253437207</t>
+          <t>1300951208</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
+          <t>ul Długa 174, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Hajnówka</t>
+          <t>Zgierz</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Niebieski Falcon sp. z o.o.</t>
+          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6955,22 +6955,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>0000010678</t>
+          <t>0000068878</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1301030396</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>ulica os. LSM 71, 20-400 Lublin</t>
+          <t>ulica Rynek 11, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Niebieski Gryf sp z oo</t>
+          <t>Bizon Instalacje S.A.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7017,22 +7017,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0000010775</t>
+          <t>0000068975</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1243595554</t>
+          <t>1291109557</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>88, 24-120 Mięćmierz</t>
+          <t>Jedności Narodowej 28, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Mięćmierz</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont sp. z o. o.</t>
+          <t>Bizon Nieruchomości SA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7079,22 +7079,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0000010872</t>
+          <t>0000069072</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1253674775</t>
+          <t>1291188746</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
+          <t>ul. Konstytucji 3 Maja 45/77, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Biała Podlaska</t>
+          <t>Karpacz</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Niebieski Ikar Sp. z o.o.</t>
+          <t>Bizon Inwestycje S. A.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2018-05-04</t>
+          <t>2018-04-05</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t/>
+          <t>0000069169</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1291267931</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
+          <t>ul Odrodzenia 62, 59-300 Lubin</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Lubin</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Niebieski Jantar SP Z O O</t>
+          <t>Bizon Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7203,22 +7203,22 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>0000011066</t>
+          <t/>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>1243833120</t>
+          <t>1291347127</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
+          <t>ulica Słowackiego 79, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Wałbrzych</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7265,22 +7265,22 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>0000011163</t>
+          <t>0000069363</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1243912316</t>
+          <t>1291426312</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Stare Miasto 156, 10-026 Olsztyn</t>
+          <t>Półwiejska 96, 61-888 Poznań</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Urody sp z oo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7327,22 +7327,22 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0000011260</t>
+          <t>0000069460</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>1243991505</t>
+          <t>1291505508</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
+          <t>ul. os. Bolesława Chrobrego 113/39, 60-681 Poznań</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Mrągowo</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia S.A.</t>
+          <t>Bizon Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7389,22 +7389,22 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0000011357</t>
+          <t>0000069557</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>1244070693</t>
+          <t>1291584695</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
+          <t>ul Główny Rynek 130, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Kalisz</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Niebieski Neon SA</t>
+          <t>Bizon Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0000011454</t>
+          <t>0000069654</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>1244149880</t>
+          <t>1291663880</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Niebieski Oaza S. A.</t>
+          <t>Bizon Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0000011551</t>
+          <t>0000069751</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>1244229076</t>
+          <t>1291743076</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>X - Twitter</t>
+          <t>mBank</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7575,22 +7575,22 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>0000011648</t>
+          <t>0000069848</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>1244308261</t>
+          <t>1291822261</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
+          <t>ul. os. Jasień 1/1, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Kluczbork</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Niebieski Rubin sp. z o.o.</t>
+          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7632,27 +7632,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0000011745</t>
+          <t>0000069945</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>1244387450</t>
+          <t>1291901457</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
+          <t>ul Bohaterów Monte Cassino 18, 81-759 Sopot</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Gorzów Wielkopolski</t>
+          <t>Sopot</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Niebieski Szafir sp z oo</t>
+          <t>Bizon Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7699,22 +7699,22 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>0000011842</t>
+          <t>0000070042</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>1244466646</t>
+          <t>1291980646</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
+          <t>35, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Międzyrzecz</t>
+          <t>Chwaszczyno</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Niebieski Tytan sp. z o. o.</t>
+          <t>Bizon Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7761,22 +7761,22 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>0000011939</t>
+          <t>0000070139</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1244545831</t>
+          <t>1292059838</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Paderewskiego 112, 25-004 Kielce</t>
+          <t>3 Maja 52, 40-096 Katowice</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Niebieski Uran Sp. z o.o.</t>
+          <t>Bizon Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7823,22 +7823,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>0000012036</t>
+          <t>0000070236</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>1244625027</t>
+          <t>1292139023</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
+          <t>ul. os. Paderewskiego 69/53, 40-282 Katowice</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Busko-Zdrój</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Niebieski Wektor SP Z O O</t>
+          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7885,22 +7885,22 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>0000012133</t>
+          <t>0000070333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>1244704212</t>
+          <t>1292218219</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
+          <t>os. Zwycięstwa 86, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Gliwice</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7942,27 +7942,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2019-01-08</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>0000012230</t>
+          <t>0000070430</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>1244783401</t>
+          <t>1292297408</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
+          <t>ulica Bocheńskiego 103, 43-100 Tychy</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Tychy</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Ochrona sp z oo</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8009,22 +8009,22 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>0000012327</t>
+          <t>0000070527</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>1244862595</t>
+          <t>1292376591</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Floriańska 180, 31-019 Kraków</t>
+          <t>Najświętszej Maryi Panny 120, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Częstochowa</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Niebieski Sokół S.A.</t>
+          <t>Bizon Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8071,22 +8071,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>0000012424</t>
+          <t>0000070624</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>1244941780</t>
+          <t>1292455787</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>ul. Długa 17/45, 31-147 Kraków</t>
+          <t>ul. 11 Listopada 137/15, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Bielsko-Biała</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł SA</t>
+          <t>Bizon Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8133,22 +8133,22 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>0000012521</t>
+          <t>0000070721</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>1245020970</t>
+          <t>1292534972</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>ul Piotrkowska 34, 90-102 Łódź</t>
+          <t>154, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Niechobrz</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran S. A.</t>
+          <t>Canyon Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8195,22 +8195,22 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>0000012618</t>
+          <t>0000070818</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>1245100166</t>
+          <t>1292614168</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>ulica Zachodnia 51, 90-402 Łódź</t>
+          <t>ulica Franciszkańska 171, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Przemyśl</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Niebieski Barycz Spółka Akcyjna</t>
+          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8252,27 +8252,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0000012715</t>
+          <t>0000070915</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>1245179357</t>
+          <t>1292693357</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Świdnicka 68, 50-066 Wrocław</t>
+          <t>Kościuszki 8, 38-500 Sanok</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Sanok</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Niebieski Noteć sp. z o.o.</t>
+          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8319,22 +8319,22 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0000012812</t>
+          <t>0000071012</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>1245258542</t>
+          <t>1292772542</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
+          <t>ul. Suraska 25/67, 15-422 Białystok</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Niebieski Pilica sp z oo</t>
+          <t>Canyon Logistyka S.A.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8381,22 +8381,22 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0000012909</t>
+          <t>0000071109</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>1245337738</t>
+          <t>1292851738</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>ul Święty Marcin 102, 61-806 Poznań</t>
+          <t>42, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Ogrodniczki</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Niebieski Narew sp. z o. o.</t>
+          <t>Canyon Handel SA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8443,22 +8443,22 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>0000013006</t>
+          <t>0000071206</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>1245416923</t>
+          <t>1292930923</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>ulica Głogowska 119, 60-734 Poznań</t>
+          <t>ulica 3 Maja 59, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Hajnówka</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka Sp. z o.o.</t>
+          <t>Canyon Usługi S. A.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8505,22 +8505,22 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>0000013103</t>
+          <t>0000071303</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>1245496112</t>
+          <t>1293010113</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Długa 136, 80-831 Gdańsk</t>
+          <t>os. LSM 76, 20-400 Lublin</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus SP Z O O</t>
+          <t>Canyon Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8567,22 +8567,22 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>0000013200</t>
+          <t>0000071400</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>1245575308</t>
+          <t>1293089304</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
+          <t>93/29, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Mięćmierz</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>0000013297</t>
+          <t>0000071497</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>1245654491</t>
+          <t>1293168498</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8691,22 +8691,22 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>0000013394</t>
+          <t>0000071594</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>1245733687</t>
+          <t>1293247683</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
+          <t>ulica Rynek Staromiejski 127, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Niebieski Granit S.A.</t>
+          <t>Canyon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8753,22 +8753,22 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>0000013491</t>
+          <t>0000071691</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1245812872</t>
+          <t>1293326879</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Mariacka 24, 40-014 Katowice</t>
+          <t>Mostowa 144, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Marmur</t>
+          <t>PPHU Canyon Reklama</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8815,22 +8815,22 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>0000013588</t>
+          <t>0000071788</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1245892061</t>
+          <t>1293406064</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
+          <t>ul. Stare Miasto 161/81, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Niebieski Syrena S. A.</t>
+          <t>Canyon Marketing SP Z O O</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8877,22 +8877,22 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>0000013685</t>
+          <t>0000071885</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>1245971257</t>
+          <t>1293485253</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
+          <t>ul Warszawska 178, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Mrągowo</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak Spółka Akcyjna</t>
+          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8939,22 +8939,22 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>0000013782</t>
+          <t>0000071982</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1246050447</t>
+          <t>1293564449</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>ulica Narutowicza 75, 20-004 Lublin</t>
+          <t>ulica Wojska Polskiego 15, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Niebieski Olimp sp. z o.o.</t>
+          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9001,22 +9001,22 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>0000013879</t>
+          <t>0000072079</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1246129634</t>
+          <t>1293643634</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Lipowa 92, 15-424 Białystok</t>
+          <t>Monte Cassino 32, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Świnoujście</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Niebieski Zorza sp z oo</t>
+          <t>Canyon Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9063,22 +9063,22 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>0000013976</t>
+          <t>0000072176</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>1256208855</t>
+          <t>1303722856</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
+          <t>ul. Rynek 49/43, 45-015 Opole</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Niebieski Krokus sp. z o. o.</t>
+          <t>Canyon Rolnictwo SA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9125,22 +9125,22 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>0000014073</t>
+          <t>0000072273</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1293802015</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
+          <t>ul Byczyńska 66, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Kluczbork</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz Sp. z o.o.</t>
+          <t>Canyon Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9182,27 +9182,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-11-07</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>0000014170</t>
+          <t>0000072370</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>1246367204</t>
+          <t>1293881204</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
+          <t>ulica Chrobrego 83, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Gorzów Wielkopolski</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Niebieski Giewont SP Z O O</t>
+          <t>Canyon Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9249,22 +9249,22 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>0000014267</t>
+          <t>0000072467</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>1246446398</t>
+          <t>1293960398</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Szeroka 160, 87-100 Toruń</t>
+          <t>30 Stycznia 100, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Międzyrzecz</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9311,22 +9311,22 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>0000014364</t>
+          <t>0000072564</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>1246525583</t>
+          <t>1304039618</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
+          <t>ul. Paderewskiego 117/5, 25-004 Kielce</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9373,22 +9373,22 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0000014461</t>
+          <t>0000072661</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>1246604779</t>
+          <t>1294118775</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
+          <t>ul 1 Maja 134, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Busko-Zdrój</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Amber Budownictwo S.A.</t>
+          <t>Canyon Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9435,22 +9435,22 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>0000014558</t>
+          <t>0000072758</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>1246683968</t>
+          <t>1294197964</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
+          <t>ulica Marszałkowska 151, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Amber Transport SA</t>
+          <t>Canyon Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9497,22 +9497,22 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0000014655</t>
+          <t>0000072855</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>1246763153</t>
+          <t>1304277186</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 25-007 Kielce</t>
+          <t>Krakowskie Przedmieście 168, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Warszawa</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Amber Spedycja S. A.</t>
+          <t>Canyon Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9559,22 +9559,22 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>0000014752</t>
+          <t>0000072952</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>1246842349</t>
+          <t>1294356345</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
+          <t>ul. Floriańska 5/57, 31-019 Kraków</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Amber Logistyka Spółka Akcyjna</t>
+          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9621,22 +9621,22 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>0000014849</t>
+          <t>0000073049</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>1246921534</t>
+          <t>1294435530</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
+          <t>ul Długa 22, 31-147 Kraków</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Kraków</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Amber Handel sp. z o.o.</t>
+          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9683,22 +9683,22 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>0000014946</t>
+          <t>0000073146</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>1247000724</t>
+          <t>1294514726</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
+          <t>os. Piotrkowska 39, 90-102 Łódź</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Amber Usługi sp z oo</t>
+          <t>Canyon Zdrowie S.A.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9745,22 +9745,22 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>0000015043</t>
+          <t>0000073243</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>1247079915</t>
+          <t>1294593915</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Krakowska 116, 45-018 Opole</t>
+          <t>Zachodnia 56, 90-402 Łódź</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Łódź</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Amber Finanse sp. z o. o.</t>
+          <t>Canyon Urody SA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9802,27 +9802,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>0000015140</t>
+          <t>0000073340</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>1247159100</t>
+          <t>1294673100</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>ul. Ozimska 133/49, 45-057 Opole</t>
+          <t>ul. Świdnicka 73/19, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>wydawca pieniądza elektroniczneog</t>
+          <t>wydawca pieniądza elektronicznego</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Amber Doradztwo Sp. z o.o.</t>
+          <t>Canyon Turystyka S. A.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9869,22 +9869,22 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>0000015237</t>
+          <t>0000073437</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>1247238294</t>
+          <t>1294752294</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
+          <t>ul Legnicka 90, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Wrocław</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Amber Szkolenia SP Z O O</t>
+          <t>Canyon Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9931,22 +9931,22 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>0000015334</t>
+          <t>0000073534</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1257317517</t>
+          <t>1304831518</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
+          <t>ulica Święty Marcin 107, 61-806 Poznań</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9993,22 +9993,22 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>0000015431</t>
+          <t>0000073631</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1294910675</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Świętojańska 4, 81-372 Gdynia</t>
+          <t>Głogowska 124, 60-734 Poznań</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Poznań</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Facebook - Meta</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10055,22 +10055,22 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>0000015528</t>
+          <t>0000073728</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>1247475864</t>
+          <t>1294989866</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
+          <t>ul. Długa 141/71, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Amber Marketing S.A.</t>
+          <t>Canyon Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10117,22 +10117,22 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>0000015625</t>
+          <t>0000073825</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>1257555085</t>
+          <t>1295069056</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
+          <t>ul Grunwaldzka 158, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Pruszków</t>
+          <t>Gdańsk</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Amber Druk SA</t>
+          <t>Canyon Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>0000015722</t>
+          <t>0000073922</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1295148241</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
+          <t>ulica Jagiellońska 175, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Piaseczno</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Amber Informatyka S. A.</t>
+          <t>Canyon Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10241,22 +10241,22 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>0000015819</t>
+          <t>0000074019</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>1247713430</t>
+          <t>2295227437</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
+          <t>Wyszyńskiego 12, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Wieliczka</t>
+          <t>Szczecin</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie Spółka Akcyjna</t>
+          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10303,22 +10303,22 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>0000015916</t>
+          <t>0000074116</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2257792655</t>
+          <t>1295306622</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
+          <t>ul. Mariacka 29/33, 40-014 Katowice</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Oświęcim</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo sp. z o.o.</t>
+          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10365,22 +10365,22 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>0000016013</t>
+          <t>0000074213</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>1295385811</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>ul Rynek 106, 38-400 Krosno</t>
+          <t>ul Warszawska 46, 40-009 Katowice</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Krosno</t>
+          <t>Katowice</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo sp z oo</t>
+          <t>Canyon Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10427,22 +10427,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0000016110</t>
+          <t>0000074310</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>1247951000</t>
+          <t>1295465007</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
+          <t>ulica Krakowskie Przedmieście 63, 20-002 Lublin</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Mielec</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Amber Produkcja sp. z o. o.</t>
+          <t>Canyon Ochrona SA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10489,22 +10489,22 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>0000016207</t>
+          <t>0000074407</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>1248030199</t>
+          <t>1295544190</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Długa 140, 58-100 Świdnica</t>
+          <t>Narutowicza 80, 20-004 Lublin</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Świdnica</t>
+          <t>Lublin</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Amber Przemysł Sp. z o.o.</t>
+          <t>Canyon Catering S. A.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10551,22 +10551,22 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>0000016304</t>
+          <t>0000074504</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>1248109386</t>
+          <t>1295623386</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>157/25, 57-300 Kłodzko</t>
+          <t>ul. Lipowa 97/85, 15-424 Białystok</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Kłodzko</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Amber Ekologia SP Z O O</t>
+          <t>Canyon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10613,22 +10613,22 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>0000016401</t>
+          <t>0000074601</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>1248188575</t>
+          <t>1295702571</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>ul Chrobrego 174, 62-200 Gniezno</t>
+          <t>ul Sienkiewicza 114, 15-092 Białystok</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Gniezno</t>
+          <t>Białystok</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
+          <t>Astra Group sp. z o.o.</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10675,22 +10675,22 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>0000016498</t>
+          <t>0000074698</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>1248267760</t>
+          <t>1295781760</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>ulica Słowiańska 11, 64-100 Leszno</t>
+          <t>ulica Gdańska 131, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Leszno</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Astra Systems sp z oo</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10737,22 +10737,22 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>0000016595</t>
+          <t>0000074795</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>1248346956</t>
+          <t>1295860956</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Gdańska 28, 83-110 Tczew</t>
+          <t>Dworcowa 148, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Tczew</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości S.A.</t>
+          <t>Astra Holding sp. z o. o.</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10799,22 +10799,22 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>0000016692</t>
+          <t>0000074892</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>1248426141</t>
+          <t>1295940141</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
+          <t>ul. Szeroka 165/47, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Wejherowo</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Amber Inwestycje SA</t>
+          <t>Astra Partners Sp. z o.o.</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10861,22 +10861,22 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>0000016789</t>
+          <t>0000074989</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>1248505337</t>
+          <t>1296019333</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>ul Głęboka 62, 43-400 Cieszyn</t>
+          <t>ul Chełmińska 2, 87-100 Toruń</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Toruń</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Amber Medycyna S. A.</t>
+          <t>Astra Polska SP Z O O</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10923,22 +10923,22 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>0000016886</t>
+          <t>0000075086</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>1248584526</t>
+          <t>1296098522</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>os. Małachowskiego 79, 42-500 Będzin</t>
+          <t>ulica 3 Maja 19, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Będzin</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Amber Zdrowie Spółka Akcyjna</t>
+          <t>Astra Enterprise spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10985,22 +10985,22 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>0000016983</t>
+          <t>0000075183</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>1248663711</t>
+          <t>1296177718</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
+          <t>Piłsudskiego 36, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Inowrocław</t>
+          <t>Rzeszów</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Amber Urody sp. z o.o.</t>
+          <t>Astra Network Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11042,27 +11042,27 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2019-02-06</t>
+          <t>2019-06-02</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>0000017080</t>
+          <t>0000075280</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>1248742907</t>
+          <t>1296256903</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
+          <t>ul. Sienkiewicza 53/9, 25-007 Kielce</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Grudziądz</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Amber Turystyka sp z oo</t>
+          <t>Apex Group S.A.</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11109,22 +11109,22 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>0000017177</t>
+          <t>0000075377</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>1248822090</t>
+          <t>1296336097</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
+          <t>ul Warszawska 70, 25-512 Kielce</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Ostróda</t>
+          <t>Kielce</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Amber Rozrywka sp. z o. o.</t>
+          <t>Apex Systems SA</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -11171,22 +11171,22 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>0000017274</t>
+          <t>0000075474</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>1248901286</t>
+          <t>1296415282</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>ulica Warszawska 147, 11-500 Giżycko</t>
+          <t>ulica Kościuszki 87, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Giżycko</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Amber Gastronomia Sp. z o.o.</t>
+          <t>Apex Holding S. A.</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11233,22 +11233,22 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>0000017371</t>
+          <t>0000075571</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>1248980475</t>
+          <t>1296494471</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Lubelska 164, 24-100 Puławy</t>
+          <t>Dąbrowszczaków 104, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Puławy</t>
+          <t>Olsztyn</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PPHU Amber Moda</t>
+          <t>P.P.H.U. Apex Partners</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11295,22 +11295,22 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>0000017468</t>
+          <t>0000075668</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>1249059667</t>
+          <t>1296573667</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>ul. Staszica 1/1, 22-400 Zamość</t>
+          <t>ul. Krakowska 121/61, 45-018 Opole</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Zamość</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Apex Polska sp. z o.o.</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11352,27 +11352,27 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>0000017565</t>
+          <t>0000075765</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>1249138852</t>
+          <t>1296652852</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>ul 3 Maja 18, 16-300 Augustów</t>
+          <t>ul Ozimska 138, 45-057 Opole</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Apex Enterprise sp z oo</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11419,22 +11419,22 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>0000017662</t>
+          <t>0000075862</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>1249218048</t>
+          <t>1296732048</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
+          <t>ulica Bohaterów Westerplatte 155, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Suwałki</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia S.A.</t>
+          <t>Apex Network sp. z o. o.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>0000017759</t>
+          <t>0000075959</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>1249297237</t>
+          <t>1296811233</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo SA</t>
+          <t>Clarity Group Sp. z o.o.</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11543,22 +11543,22 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>0000017856</t>
+          <t>0000076056</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>1249376422</t>
+          <t>1296890422</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>ul. Długa 69/53, 49-300 Brzeg</t>
+          <t>ul. Świętojańska 9/23, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Brzeg</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo S. A.</t>
+          <t>Clarity Systems SP Z O O</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11605,22 +11605,22 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>0000017953</t>
+          <t>0000076153</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>1249455618</t>
+          <t>1306969646</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>ul Rynek 86, 68-200 Żary</t>
+          <t>ul 10 Lutego 26, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Żary</t>
+          <t>Gdynia</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo Spółka Akcyjna</t>
+          <t>Clarity Holding spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11662,27 +11662,27 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2019-09-02</t>
+          <t>2019-02-09</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>0000018050</t>
+          <t>0000076250</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>1249534803</t>
+          <t>1307048836</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
+          <t>ulica Bolesława Prusa 43, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Świebodzin</t>
+          <t>Pruszków</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Amber Ochrona sp. z o.o.</t>
+          <t>Clarity Partners Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11729,22 +11729,22 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>0000018147</t>
+          <t>0000076347</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>1249613997</t>
+          <t>1297127993</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
+          <t>Kościuszki 60, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Kołobrzeg</t>
+          <t>Piaseczno</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Amber Catering sp z oo</t>
+          <t>Clarity Polska S.A.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11791,22 +11791,22 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>0000018244</t>
+          <t>0000076444</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>1249693186</t>
+          <t>1297207189</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
+          <t>ul. Sienkiewicza 77/75, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Stargard</t>
+          <t>Wieliczka</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Amber Księgowość sp. z o. o.</t>
+          <t>Clarity Enterprise SA</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11853,22 +11853,22 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>0000018341</t>
+          <t>0000076541</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>1249772371</t>
+          <t>1297286378</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>154, 27-600 Sandomierz</t>
+          <t>ul Dąbrowskiego 94, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Sandomierz</t>
+          <t>Oświęcim</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo Sp. z o.o.</t>
+          <t>Clarity Network S. A.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11915,22 +11915,22 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>0000018438</t>
+          <t>000007663</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>1249851567</t>
+          <t>1297365563</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ulica Rynek 111, 38-400 Krosno</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Ostrowiec Świętokrzyski</t>
+          <t>Krosno</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Bizon Transport SP Z O O</t>
+          <t>Core Group Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11972,27 +11972,27 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-10-11</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>000001853</t>
+          <t>0000076735</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>1249930752</t>
+          <t>1297444759</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Chmielna 8, 00-020 Warszawa</t>
+          <t>128, 39-300 Mielec</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Mielec</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
+          <t>Core Systems sp. z o.o.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12039,22 +12039,22 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>0000018632</t>
+          <t>0000076832</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>1250009942</t>
+          <t>1297523944</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
+          <t>ul. Długa 145/37, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Świdnica</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Core Holding sp z oo</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12101,22 +12101,22 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>0000018729</t>
+          <t>0000076929</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>1250089131</t>
+          <t>1307603166</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
+          <t>ul Wojska Polskiego 162, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Kłodzko</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Bizon Handel S.A.</t>
+          <t>Core Partners sp. z o. o.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12163,22 +12163,22 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0000018826</t>
+          <t>0000077026</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>1250168327</t>
+          <t>1297682329</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
+          <t>ulica Chrobrego 179, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Legionowo</t>
+          <t>Gniezno</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Bizon Usługi SA</t>
+          <t>Core Polska Sp. z o.o.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12225,22 +12225,22 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>0000018923</t>
+          <t>0000077123</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>1250247512</t>
+          <t>1297761514</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 05-270 Marki</t>
+          <t>Słowiańska 16, 64-100 Leszno</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Marki</t>
+          <t>Leszno</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Bizon Finanse S. A.</t>
+          <t>Core Enterprise SP Z O O</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12282,27 +12282,27 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2017-01-02</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>0000019020</t>
+          <t>0000077220</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>1250326708</t>
+          <t>1307840736</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
+          <t>ul. Gdańska 33/89, 83-110 Tczew</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Otwock</t>
+          <t>Tczew</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo Spółka Akcyjna</t>
+          <t>Core Network spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12349,22 +12349,22 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>0000019117</t>
+          <t>0000077317</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>1250405891</t>
+          <t>1297919895</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>ul Żeromskiego 110, 26-600 Radom</t>
+          <t>ul Sobieskiego 50, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Radom</t>
+          <t>Wejherowo</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia sp. z o.o.</t>
+          <t>Direct Group Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12411,22 +12411,22 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>0000019214</t>
+          <t>0000077414</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>1250485080</t>
+          <t>1297999084</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>ulica Tumska 127, 09-402 Płock</t>
+          <t>67, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Płock</t>
+          <t>Cieszyn</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Bizon Media sp z oo</t>
+          <t>Direct Systems S.A.</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12473,22 +12473,22 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>0000019311</t>
+          <t>0000077511</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>1250564276</t>
+          <t>1298078274</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Karmelicka 144, 31-128 Kraków</t>
+          <t>Małachowskiego 84, 42-500 Będzin</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Będzin</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
+++ b/data/xlsx/KNF_Rejestr_dostawcow_i_wydawcow_pieniadza_elektronicznego.xlsx
@@ -172,7 +172,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -234,7 +234,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -296,7 +296,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -358,7 +358,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>krajowa instytucja pieniądza elektronicznego</t>
+          <t>krajowa insttyucja pieniądza elektronicznego</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UKFN-EPI-4290/2025</t>
+          <t>UKNF-EPI-4290/2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UKNF-EPI-7300/2022</t>
+          <t>UKFN-EIP-7300/2022</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Zileona Góra</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t/>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t/>
+          <t>20171125</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t/>
+          <t>1289129807</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1289208990</t>
+          <t/>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6734,17 +6734,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>wdyawca pieniądza elektronicznego</t>
+          <t>wdyawca pineiądza elektronicznego</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UNKF-EPI-5232/2020</t>
+          <t>UKNF-EPI-5232/2020</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. A.</t>
+          <t>Delfin Turystyka . A.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2295227437</t>
+          <t>1295227437</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>1295385811</t>
+          <t>2295385811</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
